--- a/Result/profitability/2397.xlsx
+++ b/Result/profitability/2397.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.845</v>
+        <v>0.90625</v>
       </c>
       <c r="N2" t="n">
-        <v>27.495</v>
+        <v>27.33125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9087499999999999</v>
+        <v>0.87375</v>
       </c>
       <c r="N3" t="n">
-        <v>28.13</v>
+        <v>27.70375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88375</v>
+        <v>0.92875</v>
       </c>
       <c r="N4" t="n">
-        <v>29.05625</v>
+        <v>28.7275</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.87</v>
       </c>
       <c r="M5" t="n">
-        <v>0.87625</v>
+        <v>0.9262499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>29.21375</v>
+        <v>29.11875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>0.855</v>
+        <v>0.9337500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>30.51625</v>
+        <v>30.6325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0.84875</v>
+        <v>1.0075</v>
       </c>
       <c r="N7" t="n">
-        <v>31.94</v>
+        <v>32.20125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.90625</v>
+        <v>0.9725</v>
       </c>
       <c r="N8" t="n">
-        <v>33.22125</v>
+        <v>33.255</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9431,23 +9431,23 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2772</v>
+        <v>2651</v>
       </c>
       <c r="D72" t="n">
-        <v>2101</v>
+        <v>1979</v>
       </c>
       <c r="E72" t="n">
         <v>672</v>
       </c>
       <c r="F72" t="n">
-        <v>24.23</v>
+        <v>25.34</v>
       </c>
       <c r="G72" t="n">
         <v>147</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -9497,10 +9497,10 @@
         <v>-0.2584269662921348</v>
       </c>
       <c r="Y72" t="n">
-        <v>-2.800000000000001</v>
+        <v>-1.690000000000001</v>
       </c>
       <c r="Z72" t="n">
-        <v>-0.1035886052534222</v>
+        <v>-0.0625231224565298</v>
       </c>
       <c r="AA72" t="n">
         <v>-0.14</v>
@@ -9509,10 +9509,10 @@
         <v>-0.175</v>
       </c>
       <c r="AC72" t="n">
-        <v>-3.349999999999998</v>
+        <v>-2.239999999999998</v>
       </c>
       <c r="AD72" t="n">
-        <v>-0.1214648295866569</v>
+        <v>-0.08121827411167504</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>0.745</v>
       </c>
       <c r="N73" t="n">
-        <v>26.8975</v>
+        <v>27.03625</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9624,10 +9624,10 @@
         <v>-0.9696969696969697</v>
       </c>
       <c r="Y73" t="n">
-        <v>-1.16</v>
+        <v>-2.27</v>
       </c>
       <c r="Z73" t="n">
-        <v>-0.04787453569954603</v>
+        <v>-0.08958168902920283</v>
       </c>
       <c r="AA73" t="n">
         <v>-1.55</v>
@@ -9718,7 +9718,7 @@
         <v>0.7837500000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>26.5625</v>
+        <v>26.70125</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3708</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2775</v>
+      </c>
+      <c r="E75" t="n">
+        <v>933</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>286</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>274</v>
+      </c>
+      <c r="K75" t="n">
+        <v>148</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.45625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6973684210526316</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2699999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01084773001205308</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.449438202247191</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.870000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0691823899371069</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
